--- a/innolight/dist/20261025_中際旭創模型_v0.2.1.xlsx
+++ b/innolight/dist/20261025_中際旭創模型_v0.2.1.xlsx
@@ -5823,7 +5823,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6060,7 +6060,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6181,7 +6181,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6302,7 +6302,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6423,7 +6423,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6544,7 +6544,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
